--- a/data/input/custom_feature_annotations.xlsx
+++ b/data/input/custom_feature_annotations.xlsx
@@ -4,15 +4,33 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="filtering" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="additions" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="polymerase_analysis" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="feature_neighbourhoods" sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment authorId="0" ref="A1">
+      <text>
+        <t xml:space="preserve">This sheet is used for removing features from the genome coverage data frame used to make the heatmap figures. It works by filtering features either by their chromosome coordinates or by the feature name. In both cases, a valid Filter.group value must be provided. Options are: "all", "RPC", "RPC34", "RPC53", "RPC160"
+To filter by coordinates: provide Chromosome, Start, Stop and Strand values that match those of the feature you want to be removed. The Feature value is not used by the filter (i.e., can be anything you like)
+To filter by feature name: provide the name of the feature as is shown in the heatmap figure.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="64">
   <si>
     <t>Feature</t>
   </si>
@@ -95,9 +113,15 @@
     <t>Chromosome-organizing-clamp(misc_feature)</t>
   </si>
   <si>
+    <t>ETC1(misc feature)</t>
+  </si>
+  <si>
     <t>ETC2(misc feature)</t>
   </si>
   <si>
+    <t>ETC3(misc feature)</t>
+  </si>
+  <si>
     <t>ETC4(misc feature)</t>
   </si>
   <si>
@@ -110,6 +134,24 @@
     <t>ETC7(misc feature)</t>
   </si>
   <si>
+    <t>ETC8(misc feature)</t>
+  </si>
+  <si>
+    <t>regulatory_region</t>
+  </si>
+  <si>
+    <t>other_RNA</t>
+  </si>
+  <si>
+    <t>pseudogene</t>
+  </si>
+  <si>
+    <t>anti-feature</t>
+  </si>
+  <si>
+    <t>RNA.Polymerase</t>
+  </si>
+  <si>
     <t>Feature.type</t>
   </si>
   <si>
@@ -174,6 +216,12 @@
   </si>
   <si>
     <t>gene-YNCM0003W</t>
+  </si>
+  <si>
+    <t>centromere</t>
+  </si>
+  <si>
+    <t>origin of replication</t>
   </si>
 </sst>
 </file>
@@ -250,6 +298,10 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -725,8 +777,65 @@
         <v>15</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -737,36 +846,39 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.88"/>
-    <col customWidth="1" min="2" max="2" width="11.88"/>
-    <col customWidth="1" min="3" max="3" width="14.75"/>
-    <col customWidth="1" min="5" max="5" width="7.25"/>
-    <col customWidth="1" min="6" max="7" width="6.5"/>
+    <col customWidth="1" min="1" max="1" width="14.38"/>
+    <col customWidth="1" min="2" max="2" width="10.88"/>
+    <col customWidth="1" min="3" max="3" width="11.88"/>
+    <col customWidth="1" min="4" max="4" width="14.75"/>
+    <col customWidth="1" min="6" max="6" width="7.25"/>
+    <col customWidth="1" min="7" max="8" width="6.5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>33</v>
+        <v>39</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
@@ -787,171 +899,221 @@
       <c r="Z1" s="2"/>
       <c r="AA1" s="2"/>
       <c r="AB1" s="2"/>
+      <c r="AC1" s="2"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="3">
+        <v>459676.0</v>
+      </c>
+      <c r="H2" s="3">
+        <v>459796.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="3">
+        <v>366235.0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>366346.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="3">
+        <v>431129.0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>431220.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="3">
+        <v>117667.0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>118035.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="3">
+        <v>441987.0</v>
+      </c>
+      <c r="H7" s="3">
+        <v>442508.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="3">
+        <v>667288.0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>667456.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="3">
+        <v>91970.0</v>
+      </c>
+      <c r="H9" s="3">
+        <v>92027.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="15.0"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="3">
-        <v>459676.0</v>
-      </c>
-      <c r="G2" s="3">
-        <v>459796.0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="3">
-        <v>366235.0</v>
-      </c>
-      <c r="G4" s="3">
-        <v>366346.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="3">
-        <v>431129.0</v>
-      </c>
-      <c r="G5" s="3">
-        <v>431220.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="3">
-        <v>117667.0</v>
-      </c>
-      <c r="G6" s="3">
-        <v>118035.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="3">
-        <v>441987.0</v>
-      </c>
-      <c r="G7" s="3">
-        <v>442508.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="3">
-        <v>667288.0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>667456.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="3">
-        <v>91970.0</v>
-      </c>
-      <c r="G9" s="3">
-        <v>92027.0</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/data/input/custom_feature_annotations.xlsx
+++ b/data/input/custom_feature_annotations.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="66">
   <si>
     <t>Feature</t>
   </si>
@@ -137,10 +137,10 @@
     <t>ETC8(misc feature)</t>
   </si>
   <si>
-    <t>regulatory_region</t>
-  </si>
-  <si>
-    <t>other_RNA</t>
+    <t>regulatory region</t>
+  </si>
+  <si>
+    <t>other RNA</t>
   </si>
   <si>
     <t>pseudogene</t>
@@ -222,6 +222,12 @@
   </si>
   <si>
     <t>origin of replication</t>
+  </si>
+  <si>
+    <t>RPL</t>
+  </si>
+  <si>
+    <t>RPS</t>
   </si>
 </sst>
 </file>
@@ -1116,6 +1122,16 @@
         <v>63</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/data/input/custom_feature_annotations.xlsx
+++ b/data/input/custom_feature_annotations.xlsx
@@ -433,7 +433,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:Z23"/>
-  <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.66015625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.88"/>
   </cols>
@@ -783,11 +783,11 @@
   <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="17.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="6" width="14.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="6" width="14.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="18.24"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="6" width="12.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="6" width="10.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="6" width="6.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="6" width="8.23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="6" width="17.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="6" width="18.24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="6" width="16.02"/>
@@ -1071,7 +1071,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.66015625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
   </cols>

--- a/data/input/custom_feature_annotations.xlsx
+++ b/data/input/custom_feature_annotations.xlsx
@@ -271,7 +271,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -295,25 +295,25 @@
       <family val="0"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="0"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -329,6 +329,13 @@
       <color rgb="FF000000"/>
       <name val="Courier New"/>
       <family val="3"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -374,24 +381,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -412,6 +423,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -432,335 +447,347 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Z23"/>
-  <sheetFormatPr defaultColWidth="12.66015625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:Z26"/>
+  <sheetFormatPr defaultColWidth="12.6796875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.88"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="2" style="1" width="12.66"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>90907</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>91324</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>91324</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="4" t="n">
         <v>92418</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>92418</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="5" t="n">
         <f aca="false">92418+476</f>
         <v>92894</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="6" t="n">
         <v>254789</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="6" t="n">
         <v>255161</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="B6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="5" t="n">
         <f aca="false">116167-216</f>
         <v>115951</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="5" t="n">
         <f aca="false">116970+77</f>
         <v>117047</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="B7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="4" t="n">
         <v>278213</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="4" t="n">
         <v>278947</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="4" t="n">
         <v>539421</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="4" t="n">
         <v>544813</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="4" t="n">
         <v>182734</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="4" t="n">
         <v>184823</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="4" t="n">
         <v>634095</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="4" t="n">
         <v>635947</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="B11" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="B12" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="B13" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
+      <c r="B14" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
+      <c r="B15" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="s">
+      <c r="B16" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
+      <c r="B17" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="s">
+      <c r="B18" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
+      <c r="B19" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+      <c r="B20" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
+      <c r="B21" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
+      <c r="B22" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>15</v>
-      </c>
+      <c r="B23" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0"/>
+      <c r="B24" s="4"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0"/>
+      <c r="B25" s="4"/>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -779,281 +806,284 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC1048576"/>
   <sheetFormatPr defaultColWidth="12.640625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="17.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="6" width="14.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="18.24"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="6" width="12.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="6" width="10.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="6" width="8.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="6" width="17.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="6" width="18.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="6" width="16.02"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="12" style="6" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="17.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="7" width="14.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="18.24"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="12.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="10.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="7" width="8.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="7" width="17.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="7" width="18.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="7" width="16.02"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="12" style="7" width="12.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
-      <c r="V1" s="8"/>
-      <c r="W1" s="8"/>
-      <c r="X1" s="8"/>
-      <c r="Y1" s="8"/>
-      <c r="Z1" s="8"/>
-      <c r="AA1" s="8"/>
-      <c r="AB1" s="8"/>
-      <c r="AC1" s="8"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="n">
+      <c r="A2" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="9" t="n">
+      <c r="G2" s="10" t="n">
         <v>459676</v>
       </c>
-      <c r="H2" s="9" t="n">
+      <c r="H2" s="10" t="n">
         <v>459796</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="n">
+      <c r="A3" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="10" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="n">
+      <c r="A4" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" s="10" t="n">
         <v>366235</v>
       </c>
-      <c r="H4" s="9" t="n">
+      <c r="H4" s="10" t="n">
         <v>366346</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="9" t="n">
+      <c r="A5" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="10" t="n">
         <v>431129</v>
       </c>
-      <c r="H5" s="9" t="n">
+      <c r="H5" s="10" t="n">
         <v>431220</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="n">
+      <c r="A6" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="10" t="n">
         <v>117667</v>
       </c>
-      <c r="H6" s="9" t="n">
+      <c r="H6" s="10" t="n">
         <v>118035</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="9" t="n">
+      <c r="A7" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="10" t="n">
         <v>441987</v>
       </c>
-      <c r="H7" s="9" t="n">
+      <c r="H7" s="10" t="n">
         <v>442508</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="n">
+      <c r="A8" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G8" s="10" t="n">
         <v>667288</v>
       </c>
-      <c r="H8" s="9" t="n">
+      <c r="H8" s="10" t="n">
         <v>667456</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9" t="n">
+      <c r="A9" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="10" t="n">
         <v>91970</v>
       </c>
-      <c r="H9" s="9" t="n">
+      <c r="H9" s="10" t="n">
         <v>92027</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="n">
+      <c r="A10" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="K10" s="6" t="n">
+      <c r="K10" s="7" t="n">
         <v>500</v>
       </c>
     </row>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1071,28 +1101,28 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="12.66015625" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.73046875" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="11" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="11" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="11" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="11" t="s">
         <v>70</v>
       </c>
     </row>

--- a/data/input/custom_feature_annotations.xlsx
+++ b/data/input/custom_feature_annotations.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="filtering" sheetId="1" state="visible" r:id="rId2"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="70">
   <si>
     <t xml:space="preserve">Feature</t>
   </si>
@@ -162,9 +162,6 @@
   </si>
   <si>
     <t xml:space="preserve">pseudogene</t>
-  </si>
-  <si>
-    <t xml:space="preserve">anti-feature</t>
   </si>
   <si>
     <t xml:space="preserve">RNA.Polymerase</t>
@@ -771,12 +768,8 @@
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>15</v>
-      </c>
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="0"/>
@@ -823,16 +816,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>41</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>42</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>2</v>
@@ -847,13 +840,13 @@
         <v>4</v>
       </c>
       <c r="I1" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>44</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>45</v>
       </c>
       <c r="L1" s="9"/>
       <c r="M1" s="9"/>
@@ -879,16 +872,16 @@
         <v>3</v>
       </c>
       <c r="B2" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="D2" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="E2" s="10" t="s">
         <v>48</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>49</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>9</v>
@@ -905,7 +898,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -913,16 +906,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="D4" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>53</v>
-      </c>
       <c r="E4" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F4" s="10" t="s">
         <v>9</v>
@@ -939,13 +932,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>16</v>
@@ -965,13 +958,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>56</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>57</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>16</v>
@@ -991,13 +984,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C7" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>58</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>59</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>16</v>
@@ -1017,16 +1010,16 @@
         <v>3</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="E8" s="10" t="s">
         <v>61</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>62</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>21</v>
@@ -1043,16 +1036,16 @@
         <v>3</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="10" t="s">
-        <v>64</v>
-      </c>
       <c r="E9" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>9</v>
@@ -1069,13 +1062,13 @@
         <v>2</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I10" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="J10" s="7" t="s">
         <v>65</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>66</v>
       </c>
       <c r="K10" s="7" t="n">
         <v>500</v>
@@ -1101,29 +1094,29 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="12.73046875" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.7421875" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
